--- a/output/Tables/7000 steps/HIA_added_7000steps_1000replicate.xlsx
+++ b/output/Tables/7000 steps/HIA_added_7000steps_1000replicate.xlsx
@@ -1,21 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/7000 steps/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6693C396-092A-364E-9361-37CD978B595E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +150,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +202,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +271,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,91 +447,75 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>100433.687</v>
+        <v>100433.68700000001</v>
       </c>
       <c r="C2">
-        <v>98060.766</v>
+        <v>98060.766000000003</v>
       </c>
       <c r="D2">
-        <v>102788.714</v>
+        <v>102788.71400000001</v>
       </c>
       <c r="E2">
         <v>1047226.785</v>
@@ -455,20 +536,18 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>139283365934.889</v>
+        <v>139283365934.88901</v>
       </c>
       <c r="L2">
-        <v>138208196737.14</v>
+        <v>138208196737.14001</v>
       </c>
       <c r="M2">
         <v>140346554881.918</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
         <v>105719.973</v>
@@ -477,44 +556,42 @@
         <v>104036.834</v>
       </c>
       <c r="D3">
-        <v>107388.903</v>
+        <v>107388.90300000001</v>
       </c>
       <c r="E3">
         <v>94713.928</v>
       </c>
       <c r="F3">
-        <v>93540.23500000002</v>
+        <v>93540.235000000015</v>
       </c>
       <c r="G3">
-        <v>95889.54799999998</v>
+        <v>95889.547999999981</v>
       </c>
       <c r="H3">
-        <v>5888413115.284</v>
+        <v>5888413115.2840004</v>
       </c>
       <c r="I3">
-        <v>5795936473.635</v>
+        <v>5795936473.6350002</v>
       </c>
       <c r="J3">
-        <v>5982536644.451</v>
+        <v>5982536644.4510002</v>
       </c>
       <c r="K3">
         <v>12596944374.59</v>
       </c>
       <c r="L3">
-        <v>12440347551.495</v>
+        <v>12440347551.495001</v>
       </c>
       <c r="M3">
         <v>12750410686.736</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>98930.916</v>
+        <v>98930.915999999997</v>
       </c>
       <c r="C4">
         <v>97568.26400000001</v>
@@ -529,127 +606,121 @@
         <v>144099.85</v>
       </c>
       <c r="G4">
-        <v>149811.034</v>
+        <v>149811.03400000001</v>
       </c>
       <c r="H4">
-        <v>1464952576.268</v>
+        <v>1464952576.2679999</v>
       </c>
       <c r="I4">
-        <v>1444609357.985</v>
+        <v>1444609357.9849999</v>
       </c>
       <c r="J4">
-        <v>1484693526.203</v>
+        <v>1484693526.2030001</v>
       </c>
       <c r="K4">
         <v>19547078844.188</v>
       </c>
       <c r="L4">
-        <v>19168086667.793</v>
+        <v>19168086667.792999</v>
       </c>
       <c r="M4">
         <v>19927150766</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>21369.13</v>
       </c>
       <c r="C5">
-        <v>21048.097</v>
+        <v>21048.097000000002</v>
       </c>
       <c r="D5">
-        <v>21690.258</v>
+        <v>21690.258000000002</v>
       </c>
       <c r="E5">
         <v>42175.75</v>
       </c>
       <c r="F5">
-        <v>41464.348</v>
+        <v>41464.347999999998</v>
       </c>
       <c r="G5">
-        <v>42908.91499999999</v>
+        <v>42908.914999999994</v>
       </c>
       <c r="H5">
-        <v>1606947821.051</v>
+        <v>1606947821.0510001</v>
       </c>
       <c r="I5">
-        <v>1583026974.455</v>
+        <v>1583026974.4549999</v>
       </c>
       <c r="J5">
         <v>1631476929.766</v>
       </c>
       <c r="K5">
-        <v>5609039250.07</v>
+        <v>5609039250.0699997</v>
       </c>
       <c r="L5">
-        <v>5514064736.004001</v>
+        <v>5514064736.0040007</v>
       </c>
       <c r="M5">
-        <v>5707066862.353</v>
+        <v>5707066862.3529997</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>37130.557</v>
+        <v>37130.557000000001</v>
       </c>
       <c r="C6">
-        <v>36077.92999999999</v>
+        <v>36077.929999999993</v>
       </c>
       <c r="D6">
-        <v>38188.34800000001</v>
+        <v>38188.348000000013</v>
       </c>
       <c r="E6">
-        <v>58550.982</v>
+        <v>58550.982000000004</v>
       </c>
       <c r="F6">
         <v>57471.74</v>
       </c>
       <c r="G6">
-        <v>59630.156</v>
+        <v>59630.156000000003</v>
       </c>
       <c r="H6">
-        <v>625200010.714</v>
+        <v>625200010.71399999</v>
       </c>
       <c r="I6">
-        <v>607573919.385</v>
+        <v>607573919.38499999</v>
       </c>
       <c r="J6">
-        <v>642837252.1370001</v>
+        <v>642837252.13700008</v>
       </c>
       <c r="K6">
-        <v>7786786185.580999</v>
+        <v>7786786185.5809994</v>
       </c>
       <c r="L6">
-        <v>7642615267.373001</v>
+        <v>7642615267.3730011</v>
       </c>
       <c r="M6">
-        <v>7931705282.545</v>
+        <v>7931705282.5450001</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>385587.676</v>
+        <v>385587.67599999998</v>
       </c>
       <c r="C7">
         <v>382389.245</v>
       </c>
       <c r="D7">
-        <v>388788.302</v>
+        <v>388788.30200000003</v>
       </c>
       <c r="E7">
         <v>123645.554</v>
@@ -673,69 +744,65 @@
         <v>16445095347.237</v>
       </c>
       <c r="L7">
-        <v>16174364048.074</v>
+        <v>16174364048.073999</v>
       </c>
       <c r="M7">
-        <v>16716296454.207</v>
+        <v>16716296454.207001</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
-        <v>648738.252</v>
+        <v>648738.25199999998</v>
       </c>
       <c r="C8">
-        <v>641120.3699999999</v>
+        <v>641120.36999999988</v>
       </c>
       <c r="D8">
-        <v>656319.0109999999</v>
+        <v>656319.01099999994</v>
       </c>
       <c r="E8">
-        <v>466057.8470000001</v>
+        <v>466057.84700000013</v>
       </c>
       <c r="F8">
-        <v>458173.015</v>
+        <v>458173.01500000001</v>
       </c>
       <c r="G8">
-        <v>473921.085</v>
+        <v>473921.08500000002</v>
       </c>
       <c r="H8">
-        <v>9585513523.317001</v>
+        <v>9585513523.3170013</v>
       </c>
       <c r="I8">
         <v>9431146725.460001</v>
       </c>
       <c r="J8">
-        <v>9741544352.556999</v>
+        <v>9741544352.5569992</v>
       </c>
       <c r="K8">
         <v>61984944001.666</v>
       </c>
       <c r="L8">
-        <v>60939478270.739</v>
+        <v>60939478270.738998</v>
       </c>
       <c r="M8">
-        <v>63032630051.841</v>
+        <v>63032630051.841003</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>749171.939</v>
+        <v>749171.93900000001</v>
       </c>
       <c r="C9">
-        <v>739181.1360000001</v>
+        <v>739181.13600000006</v>
       </c>
       <c r="D9">
-        <v>759107.7250000001</v>
+        <v>759107.72500000009</v>
       </c>
       <c r="E9">
         <v>1513284.632</v>
@@ -747,16 +814,16 @@
         <v>1529218.179</v>
       </c>
       <c r="H9">
-        <v>9585513523.317001</v>
+        <v>9585513523.3170013</v>
       </c>
       <c r="I9">
         <v>9431146725.460001</v>
       </c>
       <c r="J9">
-        <v>9741544352.556999</v>
+        <v>9741544352.5569992</v>
       </c>
       <c r="K9">
-        <v>201268309936.555</v>
+        <v>201268309936.55499</v>
       </c>
       <c r="L9">
         <v>199147675007.879</v>
